--- a/bills/JXZFSP/-5464739297/3a9dcfd46768e7fa255ad70fec543f3f44daea79a5d1d702481d965f0f9525e3/bill-current.xlsx
+++ b/bills/JXZFSP/-5464739297/3a9dcfd46768e7fa255ad70fec543f3f44daea79a5d1d702481d965f0f9525e3/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/12 16:31:41</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>150000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17857.14</t>
+          <t>150000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17857.14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>17857.14</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.14</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5464739297/3a9dcfd46768e7fa255ad70fec543f3f44daea79a5d1d702481d965f0f9525e3/bill-current.xlsx
+++ b/bills/JXZFSP/-5464739297/3a9dcfd46768e7fa255ad70fec543f3f44daea79a5d1d702481d965f0f9525e3/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/12 14:43:33</t>
+          <t>07/26 12:05:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17857.14</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -202,12 +202,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/12 16:31:41</t>
+          <t>07/26 12:05:20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17857</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -242,7 +242,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -254,7 +254,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17857.14</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
@@ -266,7 +266,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17857</t>
+          <t>388</t>
         </is>
       </c>
     </row>
@@ -278,7 +278,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>11516.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5464739297/3a9dcfd46768e7fa255ad70fec543f3f44daea79a5d1d702481d965f0f9525e3/bill-current.xlsx
+++ b/bills/JXZFSP/-5464739297/3a9dcfd46768e7fa255ad70fec543f3f44daea79a5d1d702481d965f0f9525e3/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>07/26 13:39:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11516</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>07/26 12:05:20</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>388</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>11516.76</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5464739297/3a9dcfd46768e7fa255ad70fec543f3f44daea79a5d1d702481d965f0f9525e3/bill-current.xlsx
+++ b/bills/JXZFSP/-5464739297/3a9dcfd46768e7fa255ad70fec543f3f44daea79a5d1d702481d965f0f9525e3/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/26 12:05:06</t>
+          <t>07/28 12:20:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/26 13:39:00</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11516</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/26 12:05:20</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>11904.76</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>11904</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5464739297/3a9dcfd46768e7fa255ad70fec543f3f44daea79a5d1d702481d965f0f9525e3/bill-current.xlsx
+++ b/bills/JXZFSP/-5464739297/3a9dcfd46768e7fa255ad70fec543f3f44daea79a5d1d702481d965f0f9525e3/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/28 14:06:41</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11904.76</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.76</t>
         </is>
       </c>
     </row>
